--- a/src/assets/employees/faten.xlsx
+++ b/src/assets/employees/faten.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -559,9 +559,29 @@
         <v>2026-09-11</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>faten</v>
+      </c>
+      <c r="B9" t="str">
+        <v>achat</v>
+      </c>
+      <c r="C9" t="str">
+        <v>sonede</v>
+      </c>
+      <c r="D9" t="str">
+        <v>vérification et compréhension redondance logicielle pour sonede</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-09-17</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>